--- a/originales/respuestas/2025/01. Calificadas/root/Instituto Distrital Para La Protección De La Niñez Y La Juventud.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Instituto Distrital Para La Protección De La Niñez Y La Juventud.xlsx
@@ -413,7 +413,7 @@
     <t>¿Su entidad ha puesto a disposición de todos formación orientada al fortalecimiento de capacidades en innovación?</t>
   </si>
   <si>
-    <t>Pregunta 30</t>
+    <t>Pregunta 30.</t>
   </si>
   <si>
     <t>¿Qué estrategias o iniciativas ha implementado su entidad para fomentar una cultura de innovación entre sus funcionarios y contratistas?</t>
@@ -422,7 +422,7 @@
     <t>Programas de sensibilización sobre innovación pública., Espacios de ideación y cocreación con los equipos internos., Procesos de formación o capacitaciones en metodologías de innovación.</t>
   </si>
   <si>
-    <t>Pregunta 31</t>
+    <t>Pregunta 31.</t>
   </si>
   <si>
     <t>¿De qué manera ha incentivado su entidad la participación de los funcionarios y contratistas en procesos de innovación?</t>
@@ -5738,7 +5738,7 @@
       <c r="C18" s="11">
         <v>17.0</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="12" t="s">
         <v>128</v>
       </c>
       <c r="E18" s="10"/>
@@ -5781,7 +5781,7 @@
       <c r="C19" s="11">
         <v>18.0</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="12" t="s">
         <v>131</v>
       </c>
       <c r="E19" s="10"/>
